--- a/academias/Biología - Estadisticos 20232.xlsx
+++ b/academias/Biología - Estadisticos 20232.xlsx
@@ -683,7 +683,7 @@
         <v>8.6</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -811,19 +811,19 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>86.5</v>
+        <v>89.2</v>
       </c>
       <c r="H10" s="1">
-        <v>13.5</v>
+        <v>10.8</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -846,19 +846,19 @@
         <v>37</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>78.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="H11" s="1">
-        <v>21.6</v>
+        <v>13.5</v>
       </c>
       <c r="I11" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -878,19 +878,19 @@
         <v>294</v>
       </c>
       <c r="E12">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F12">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G12" s="1">
-        <v>90.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="H12" s="1">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="I12" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1114,16 +1114,16 @@
         <v>455</v>
       </c>
       <c r="E19">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F19">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G19" s="1">
-        <v>87.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="H19" s="1">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
       <c r="I19" s="2">
         <v>8.199999999999999</v>
@@ -1200,25 +1200,25 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>21.9</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1232,25 +1232,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>21.9</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1267,25 +1267,25 @@
         <v>29</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>89.7</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>10.3</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1302,25 +1302,25 @@
         <v>42</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1337,25 +1337,25 @@
         <v>35</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>8.6</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1372,25 +1372,25 @@
         <v>45</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F7">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1407,25 +1407,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>3.2</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1442,25 +1442,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1477,25 +1477,25 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J10">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1512,25 +1512,25 @@
         <v>37</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F11">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>8.1</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1544,25 +1544,25 @@
         <v>294</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="F12">
-        <v>294</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1579,25 +1579,25 @@
         <v>23</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1614,25 +1614,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>19.4</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J14">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1649,25 +1649,25 @@
         <v>20</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1">
+        <v>80</v>
+      </c>
+      <c r="H15" s="1">
         <v>20</v>
       </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100</v>
-      </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1684,25 +1684,25 @@
         <v>25</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J16">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1719,25 +1719,25 @@
         <v>30</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J17">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1751,25 +1751,25 @@
         <v>129</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F18">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>10.9</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1780,25 +1780,25 @@
         <v>455</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="F19">
-        <v>455</v>
+        <v>36</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>7.9</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1866,19 +1866,19 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>71.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>28.1</v>
+        <v>21.9</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1898,19 +1898,19 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>71.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>28.1</v>
+        <v>21.9</v>
       </c>
       <c r="I3" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1933,16 +1933,16 @@
         <v>29</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
       <c r="H4" s="1">
-        <v>13.8</v>
+        <v>10.3</v>
       </c>
       <c r="I4" s="2">
         <v>7.8</v>
@@ -2015,7 +2015,7 @@
         <v>8.6</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2038,16 +2038,16 @@
         <v>45</v>
       </c>
       <c r="E7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>93.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="I7" s="2">
         <v>8.300000000000001</v>
@@ -2073,19 +2073,19 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>90.3</v>
+        <v>96.8</v>
       </c>
       <c r="H8" s="1">
-        <v>9.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2120,7 +2120,7 @@
         <v>5.3</v>
       </c>
       <c r="I9" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2143,19 +2143,19 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>86.5</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2178,19 +2178,19 @@
         <v>37</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="H11" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="I11" s="2">
         <v>8</v>
-      </c>
-      <c r="G11" s="1">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="H11" s="1">
-        <v>21.6</v>
-      </c>
-      <c r="I11" s="2">
-        <v>6.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2210,19 +2210,19 @@
         <v>294</v>
       </c>
       <c r="E12">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F12">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>90.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>9.9</v>
+        <v>5.1</v>
       </c>
       <c r="I12" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>23</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>82.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="H13" s="1">
-        <v>17.4</v>
+        <v>13</v>
       </c>
       <c r="I13" s="2">
         <v>7.8</v>
@@ -2292,7 +2292,7 @@
         <v>19.4</v>
       </c>
       <c r="I14" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2315,19 +2315,19 @@
         <v>20</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H15" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I15" s="2">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2350,16 +2350,16 @@
         <v>25</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H16" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I16" s="2">
         <v>9.199999999999999</v>
@@ -2397,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2417,19 +2417,19 @@
         <v>129</v>
       </c>
       <c r="E18">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F18">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
-        <v>86.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>13.2</v>
+        <v>10.9</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2446,19 +2446,19 @@
         <v>455</v>
       </c>
       <c r="E19">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="F19">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="G19" s="1">
-        <v>87.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>12.1</v>
+        <v>7.9</v>
       </c>
       <c r="I19" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J19">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20232.xlsx
+++ b/academias/Biología - Estadisticos 20232.xlsx
@@ -1866,19 +1866,19 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>78.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1898,19 +1898,19 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>78.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1933,19 +1933,19 @@
         <v>29</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>89.7</v>
+        <v>82.8</v>
       </c>
       <c r="H4" s="1">
-        <v>10.3</v>
+        <v>17.2</v>
       </c>
       <c r="I4" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1968,19 +1968,19 @@
         <v>42</v>
       </c>
       <c r="E5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="H5" s="1">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I5" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2003,19 +2003,19 @@
         <v>35</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="H6" s="1">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="I6" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2038,19 +2038,19 @@
         <v>45</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>95.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="H7" s="1">
-        <v>4.4</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2073,19 +2073,19 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>96.8</v>
+        <v>90.3</v>
       </c>
       <c r="H8" s="1">
-        <v>3.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2120,7 +2120,7 @@
         <v>5.3</v>
       </c>
       <c r="I9" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2178,19 +2178,19 @@
         <v>37</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2210,19 +2210,19 @@
         <v>294</v>
       </c>
       <c r="E12">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="F12">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G12" s="1">
-        <v>94.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="H12" s="1">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="I12" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2245,19 +2245,19 @@
         <v>23</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>87</v>
+        <v>91.3</v>
       </c>
       <c r="H13" s="1">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I13" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2280,19 +2280,19 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>80.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="H14" s="1">
-        <v>19.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I14" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2315,19 +2315,19 @@
         <v>20</v>
       </c>
       <c r="E15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H15" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2362,7 +2362,7 @@
         <v>4</v>
       </c>
       <c r="I16" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2397,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2417,19 +2417,19 @@
         <v>129</v>
       </c>
       <c r="E18">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F18">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>89.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="H18" s="1">
-        <v>10.9</v>
+        <v>6.2</v>
       </c>
       <c r="I18" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2446,19 +2446,19 @@
         <v>455</v>
       </c>
       <c r="E19">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="F19">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G19" s="1">
-        <v>92.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>7.9</v>
+        <v>6.6</v>
       </c>
       <c r="I19" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
